--- a/results/conformal_results.xlsx
+++ b/results/conformal_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>setting</t>
   </si>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -512,6 +512,70 @@
         <v>0.0528452249746017</v>
       </c>
     </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>0.9</v>
+      </c>
+      <c r="D4">
+        <v>0.9206137424949966</v>
+      </c>
+      <c r="E4">
+        <v>0.0206137424949965</v>
+      </c>
+      <c r="F4">
+        <v>0.2879557720271181</v>
+      </c>
+      <c r="G4">
+        <v>0.6376509864622688</v>
+      </c>
+      <c r="H4">
+        <v>0.5973938277093677</v>
+      </c>
+      <c r="I4">
+        <v>0.0045853322164198</v>
+      </c>
+      <c r="J4">
+        <v>0.0528452249746017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0.9</v>
+      </c>
+      <c r="D5">
+        <v>0.8992661774516344</v>
+      </c>
+      <c r="E5">
+        <v>0.0007338225483656</v>
+      </c>
+      <c r="F5">
+        <v>0.2600354911681655</v>
+      </c>
+      <c r="G5">
+        <v>0.7494309803115121</v>
+      </c>
+      <c r="H5">
+        <v>0.7480655976936885</v>
+      </c>
+      <c r="I5">
+        <v>0.0045853322164198</v>
+      </c>
+      <c r="J5">
+        <v>0.0528452249746017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/conformal_results.xlsx
+++ b/results/conformal_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>setting</t>
   </si>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -576,6 +576,38 @@
         <v>0.0528452249746017</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>0.9</v>
+      </c>
+      <c r="D6">
+        <v>0.8992661774516344</v>
+      </c>
+      <c r="E6">
+        <v>0.0007338225483656</v>
+      </c>
+      <c r="F6">
+        <v>0.2453644617478672</v>
+      </c>
+      <c r="G6">
+        <v>0.7599383897676643</v>
+      </c>
+      <c r="H6">
+        <v>0.7586126806351655</v>
+      </c>
+      <c r="I6">
+        <v>0.0045853322164198</v>
+      </c>
+      <c r="J6">
+        <v>0.0528452249746017</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/conformal_results.xlsx
+++ b/results/conformal_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>setting</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>conformal_acp_lags96_modellinear_cpacp_a0.1_cw200_seed0_modeonline_debug-0_M0</t>
+  </si>
+  <si>
+    <t>exchange_rate.csv_lags96_modellinear_cpacp_modeonline_seed0</t>
   </si>
   <si>
     <t>acp</t>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -453,7 +456,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0.9</v>
@@ -485,7 +488,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0.9</v>
@@ -517,7 +520,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>0.9</v>
@@ -549,7 +552,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>0.9</v>
@@ -581,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>0.9</v>
@@ -606,6 +609,38 @@
       </c>
       <c r="J6">
         <v>0.0528452249746017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>0.9</v>
+      </c>
+      <c r="D7">
+        <v>0.8992661774516344</v>
+      </c>
+      <c r="E7">
+        <v>0.0007338225483656</v>
+      </c>
+      <c r="F7">
+        <v>0.1661110973601656</v>
+      </c>
+      <c r="G7">
+        <v>0.8222121396994246</v>
+      </c>
+      <c r="H7">
+        <v>0.82115514915475</v>
+      </c>
+      <c r="I7">
+        <v>0.0027498955562279</v>
+      </c>
+      <c r="J7">
+        <v>0.041426416885063</v>
       </c>
     </row>
   </sheetData>
